--- a/샘플_신청데이터_10건.xlsx
+++ b/샘플_신청데이터_10건.xlsx
@@ -589,7 +589,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TTA-2026-A0117</t>
+          <t>AI202600001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -672,8 +672,6 @@
           <t>직성제출</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>인공지능 신뢰성(CAT) 인증</t>
@@ -699,12 +697,11 @@
           <t>미동의</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TTA-2026-A0118</t>
+          <t>AI202600002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -792,7 +789,6 @@
           <t>meditech-spec.pdf</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>GS인증</t>
@@ -827,7 +823,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TTA-2026-A0119</t>
+          <t>AI202600003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -910,14 +906,11 @@
           <t>직성제출</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>field-test-report.zip</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>동의</t>
@@ -933,12 +926,11 @@
           <t>미동의</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TTA-2026-A0120</t>
+          <t>AI202600004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1021,8 +1013,6 @@
           <t>직성제출</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1048,12 +1038,11 @@
           <t>동의</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TTA-2026-A0121</t>
+          <t>AI202600005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1141,9 +1130,6 @@
           <t>lawndata-spec.pdf</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>동의</t>
@@ -1168,7 +1154,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTA-2026-A0122</t>
+          <t>AI202600006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1251,8 +1237,6 @@
           <t>직성제출</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>GS인증</t>
@@ -1278,12 +1262,11 @@
           <t>동의</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TTA-2026-A0123</t>
+          <t>AI202600007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1366,10 +1349,6 @@
           <t>직성제출</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>동의</t>
@@ -1385,12 +1364,11 @@
           <t>미동의</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TTA-2026-A0124</t>
+          <t>AI202600008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1517,7 +1495,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTA-2026-A0125</t>
+          <t>AI202600009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1600,8 +1578,6 @@
           <t>직성제출</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>기타</t>
@@ -1627,12 +1603,11 @@
           <t>동의</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TTA-2026-A0126</t>
+          <t>AI202600010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1720,7 +1695,6 @@
           <t>biosense-spec.pdf</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>GS인증</t>
@@ -1803,7 +1777,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TTA-2026-A0117</t>
+          <t>AI202600001</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1828,7 +1802,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TTA-2026-A0117</t>
+          <t>AI202600001</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1853,7 +1827,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TTA-2026-A0118</t>
+          <t>AI202600002</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1878,7 +1852,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TTA-2026-A0119</t>
+          <t>AI202600003</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1903,7 +1877,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TTA-2026-A0119</t>
+          <t>AI202600003</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1928,7 +1902,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTA-2026-A0119</t>
+          <t>AI202600003</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1953,7 +1927,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TTA-2026-A0120</t>
+          <t>AI202600004</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1978,7 +1952,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TTA-2026-A0121</t>
+          <t>AI202600005</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2003,7 +1977,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTA-2026-A0122</t>
+          <t>AI202600006</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2028,7 +2002,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TTA-2026-A0122</t>
+          <t>AI202600006</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2053,7 +2027,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTA-2026-A0123</t>
+          <t>AI202600007</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2078,7 +2052,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTA-2026-A0124</t>
+          <t>AI202600008</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2103,7 +2077,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTA-2026-A0124</t>
+          <t>AI202600008</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2128,7 +2102,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TTA-2026-A0125</t>
+          <t>AI202600009</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2153,7 +2127,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TTA-2026-A0126</t>
+          <t>AI202600010</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2328,7 +2302,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TTA-2026-A0117</t>
+          <t>AI202600001</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2374,8 +2348,6 @@
           <t>Docker, CUDA 12.1, PyTorch 2.x</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>KoBERT-base</t>
@@ -2386,10 +2358,6 @@
           <t>전이학습 + 자체 문서분류 Head</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>텍스트 본문 및 메타데이터</t>
@@ -2405,12 +2373,11 @@
           <t>모델평가리포트.zip</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TTA-2026-A0117</t>
+          <t>AI202600001</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2466,12 +2433,6 @@
           <t>학습 파이프라인 사내 Git 관리, BSD 라이선스</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>분류 결과 및 업무량 지표</t>
@@ -2482,13 +2443,11 @@
           <t>우선순위 등급</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TTA-2026-A0118</t>
+          <t>AI202600002</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2544,12 +2503,6 @@
           <t>내부 재현 파이프라인 문서화, MIT 라이선스 백본</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>DICOM 영상</t>
@@ -2574,7 +2527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TTA-2026-A0118</t>
+          <t>AI202600002</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2620,18 +2573,11 @@
           <t>REST API, HTTPS, 사내 프록시 경유</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>OpenAI gpt-4o-mini</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>탐지 결과 JSON, 임상 메모</t>
@@ -2642,13 +2588,11 @@
           <t>판독 초안 텍스트</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TTA-2026-A0119</t>
+          <t>AI202600003</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2694,11 +2638,6 @@
           <t>JetPack 6.x, Linux for Tegra</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jetson Orin Nano / L4T R36</t>
@@ -2709,7 +2648,6 @@
           <t>TensorRT FP16 엔진</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>잎 영상 및 환경 센서값</t>
@@ -2720,7 +2658,6 @@
           <t>병해충 분류 및 심각도</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>dataflow-a0119.pdf</t>
@@ -2730,7 +2667,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TTA-2026-A0120</t>
+          <t>AI202600004</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2776,8 +2713,6 @@
           <t>Kubernetes, ONNX Runtime</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Whisper-large-v3</t>
@@ -2788,10 +2723,6 @@
           <t>도메인 파인튜닝(콜센터 음성 4천 시간)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>음성 스트림</t>
@@ -2802,13 +2733,11 @@
           <t>화자별 전사 텍스트</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TTA-2026-A0120</t>
+          <t>AI202600004</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2854,18 +2783,11 @@
           <t>REST API, HTTPS</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Claude Haiku 4.5</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>전사 텍스트</t>
@@ -2876,13 +2798,11 @@
           <t>요약문 및 후속조치 목록</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TTA-2026-A0121</t>
+          <t>AI202600005</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2928,13 +2848,6 @@
           <t>Kubernetes, Elasticsearch 8.x, vLLM</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>① bge-m3 임베딩 ② 벡터+키워드 하이브리드 검색 ③ 자체 재순위화 모델 ④ 외부 LLM 요약</t>
@@ -2964,7 +2877,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTA-2026-A0122</t>
+          <t>AI202600006</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3020,12 +2933,6 @@
           <t>학습 코드 사내 저장소, Apache-2.0 프레임워크</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>라인 카메라 영상</t>
@@ -3036,13 +2943,11 @@
           <t>결함 위치·유형·등급</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TTA-2026-A0123</t>
+          <t>AI202600007</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3088,8 +2993,6 @@
           <t>Docker, CUDA 12.1, PyTorch 2.x</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Prophet + LightGBM 앙상블</t>
@@ -3100,10 +3003,6 @@
           <t>자체 판매데이터 파인튜닝</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>판매·기상·프로모션 데이터</t>
@@ -3128,7 +3027,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTA-2026-A0124</t>
+          <t>AI202600008</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3174,11 +3073,6 @@
           <t>JetPack 6.x, Linux for Tegra</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Jetson AGX Orin / L4T R36</t>
@@ -3189,7 +3083,6 @@
           <t>TensorRT INT8 엔진</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CCTV 스트림 영상</t>
@@ -3200,7 +3093,6 @@
           <t>위험행동 분류 및 경보 신호</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>dataflow-a0124.pdf</t>
@@ -3210,7 +3102,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTA-2026-A0125</t>
+          <t>AI202600009</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3256,13 +3148,6 @@
           <t>Kubernetes, Triton, gRPC</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>① 자체 STT(Whisper 파인튜닝) 전사 ② 언어 감지 ③ 외부 번역 API 호출 ④ 자막 동기화 렌더링</t>
@@ -3278,7 +3163,6 @@
           <t>원문·번역 자막</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>dataflow-a0125.pdf</t>
@@ -3288,7 +3172,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTA-2026-A0126</t>
+          <t>AI202600010</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3344,11 +3228,6 @@
           <t>내부 재현 파이프라인 문서화, MIT 라이선스 백본</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>심전도 파형 및 환자 메타</t>

--- a/샘플_신청데이터_10건.xlsx
+++ b/샘플_신청데이터_10건.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="410">
   <si>
     <t>접수번호</t>
   </si>
@@ -45,7 +45,7 @@
     <t>이메일</t>
   </si>
   <si>
-    <t>제품명</t>
+    <t>제품 또는 서비스 모델명</t>
   </si>
   <si>
     <t>제공형태</t>
@@ -595,9 +595,6 @@
   </si>
   <si>
     <t>연번</t>
-  </si>
-  <si>
-    <t>모델명</t>
   </si>
   <si>
     <t>세부품명번호</t>
@@ -2438,13 +2435,13 @@
         <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2455,13 +2452,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" t="s">
         <v>196</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>197</v>
-      </c>
-      <c r="E2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2472,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" t="s">
         <v>199</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>200</v>
-      </c>
-      <c r="E3" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2489,13 +2486,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" t="s">
         <v>202</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>203</v>
-      </c>
-      <c r="E4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2506,13 +2503,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" t="s">
         <v>205</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>206</v>
-      </c>
-      <c r="E5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2523,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" t="s">
         <v>208</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>209</v>
-      </c>
-      <c r="E6" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2540,13 +2537,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" t="s">
         <v>211</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>212</v>
-      </c>
-      <c r="E7" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2557,13 +2554,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" t="s">
         <v>214</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>215</v>
-      </c>
-      <c r="E8" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2574,13 +2571,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" t="s">
         <v>217</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>218</v>
-      </c>
-      <c r="E9" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2591,13 +2588,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" t="s">
         <v>220</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>221</v>
-      </c>
-      <c r="E10" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2608,13 +2605,13 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" t="s">
         <v>223</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>224</v>
-      </c>
-      <c r="E11" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2625,13 +2622,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" t="s">
         <v>226</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>227</v>
-      </c>
-      <c r="E12" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2642,13 +2639,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" t="s">
         <v>229</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>230</v>
-      </c>
-      <c r="E13" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2659,13 +2656,13 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" t="s">
         <v>232</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>233</v>
-      </c>
-      <c r="E14" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2676,13 +2673,13 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" t="s">
         <v>235</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>236</v>
-      </c>
-      <c r="E15" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2693,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" t="s">
         <v>238</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>239</v>
-      </c>
-      <c r="E16" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2720,70 +2717,70 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -2794,67 +2791,67 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" t="s">
         <v>263</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>264</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>265</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>266</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>267</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>268</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>269</v>
       </c>
-      <c r="J2" t="s">
-        <v>270</v>
-      </c>
       <c r="K2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M2" t="s">
         <v>271</v>
       </c>
-      <c r="L2" t="s">
-        <v>271</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>272</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>270</v>
+      </c>
+      <c r="P2" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>270</v>
+      </c>
+      <c r="R2" t="s">
+        <v>270</v>
+      </c>
+      <c r="S2" t="s">
+        <v>270</v>
+      </c>
+      <c r="T2" t="s">
+        <v>270</v>
+      </c>
+      <c r="U2" t="s">
         <v>273</v>
       </c>
-      <c r="O2" t="s">
-        <v>271</v>
-      </c>
-      <c r="P2" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>271</v>
-      </c>
-      <c r="R2" t="s">
-        <v>271</v>
-      </c>
-      <c r="S2" t="s">
-        <v>271</v>
-      </c>
-      <c r="T2" t="s">
-        <v>271</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>274</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>275</v>
-      </c>
-      <c r="W2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -2865,67 +2862,67 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" t="s">
         <v>277</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>278</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>279</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>280</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>281</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>282</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>283</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>284</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>285</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>270</v>
+      </c>
+      <c r="N3" t="s">
+        <v>270</v>
+      </c>
+      <c r="O3" t="s">
+        <v>270</v>
+      </c>
+      <c r="P3" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>270</v>
+      </c>
+      <c r="R3" t="s">
+        <v>270</v>
+      </c>
+      <c r="S3" t="s">
+        <v>270</v>
+      </c>
+      <c r="T3" t="s">
+        <v>270</v>
+      </c>
+      <c r="U3" t="s">
         <v>286</v>
       </c>
-      <c r="M3" t="s">
-        <v>271</v>
-      </c>
-      <c r="N3" t="s">
-        <v>271</v>
-      </c>
-      <c r="O3" t="s">
-        <v>271</v>
-      </c>
-      <c r="P3" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>271</v>
-      </c>
-      <c r="R3" t="s">
-        <v>271</v>
-      </c>
-      <c r="S3" t="s">
-        <v>271</v>
-      </c>
-      <c r="T3" t="s">
-        <v>271</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>287</v>
       </c>
-      <c r="V3" t="s">
-        <v>288</v>
-      </c>
       <c r="W3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -2936,67 +2933,67 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" t="s">
         <v>289</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>290</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>291</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>292</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I4" t="s">
         <v>293</v>
       </c>
-      <c r="H4" t="s">
-        <v>282</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>294</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>295</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>296</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
+        <v>270</v>
+      </c>
+      <c r="N4" t="s">
+        <v>270</v>
+      </c>
+      <c r="O4" t="s">
+        <v>270</v>
+      </c>
+      <c r="P4" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>270</v>
+      </c>
+      <c r="R4" t="s">
+        <v>270</v>
+      </c>
+      <c r="S4" t="s">
+        <v>270</v>
+      </c>
+      <c r="T4" t="s">
+        <v>270</v>
+      </c>
+      <c r="U4" t="s">
         <v>297</v>
       </c>
-      <c r="M4" t="s">
-        <v>271</v>
-      </c>
-      <c r="N4" t="s">
-        <v>271</v>
-      </c>
-      <c r="O4" t="s">
-        <v>271</v>
-      </c>
-      <c r="P4" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>271</v>
-      </c>
-      <c r="R4" t="s">
-        <v>271</v>
-      </c>
-      <c r="S4" t="s">
-        <v>271</v>
-      </c>
-      <c r="T4" t="s">
-        <v>271</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>298</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>299</v>
-      </c>
-      <c r="W4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -3007,67 +3004,67 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
         <v>301</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>302</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>303</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>304</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>305</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>306</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>307</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>270</v>
+      </c>
+      <c r="L5" t="s">
+        <v>270</v>
+      </c>
+      <c r="M5" t="s">
+        <v>270</v>
+      </c>
+      <c r="N5" t="s">
+        <v>270</v>
+      </c>
+      <c r="O5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P5" t="s">
         <v>308</v>
       </c>
-      <c r="K5" t="s">
-        <v>271</v>
-      </c>
-      <c r="L5" t="s">
-        <v>271</v>
-      </c>
-      <c r="M5" t="s">
-        <v>271</v>
-      </c>
-      <c r="N5" t="s">
-        <v>271</v>
-      </c>
-      <c r="O5" t="s">
-        <v>271</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
+        <v>270</v>
+      </c>
+      <c r="R5" t="s">
+        <v>270</v>
+      </c>
+      <c r="S5" t="s">
+        <v>270</v>
+      </c>
+      <c r="T5" t="s">
+        <v>270</v>
+      </c>
+      <c r="U5" t="s">
         <v>309</v>
       </c>
-      <c r="Q5" t="s">
-        <v>271</v>
-      </c>
-      <c r="R5" t="s">
-        <v>271</v>
-      </c>
-      <c r="S5" t="s">
-        <v>271</v>
-      </c>
-      <c r="T5" t="s">
-        <v>271</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>310</v>
       </c>
-      <c r="V5" t="s">
-        <v>311</v>
-      </c>
       <c r="W5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -3078,67 +3075,67 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D6" t="s">
         <v>312</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>313</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>314</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>315</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>316</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>317</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>318</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>270</v>
+      </c>
+      <c r="L6" t="s">
+        <v>270</v>
+      </c>
+      <c r="M6" t="s">
+        <v>270</v>
+      </c>
+      <c r="N6" t="s">
+        <v>270</v>
+      </c>
+      <c r="O6" t="s">
+        <v>270</v>
+      </c>
+      <c r="P6" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q6" t="s">
         <v>319</v>
       </c>
-      <c r="K6" t="s">
-        <v>271</v>
-      </c>
-      <c r="L6" t="s">
-        <v>271</v>
-      </c>
-      <c r="M6" t="s">
-        <v>271</v>
-      </c>
-      <c r="N6" t="s">
-        <v>271</v>
-      </c>
-      <c r="O6" t="s">
-        <v>271</v>
-      </c>
-      <c r="P6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>320</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
+        <v>270</v>
+      </c>
+      <c r="T6" t="s">
+        <v>270</v>
+      </c>
+      <c r="U6" t="s">
         <v>321</v>
       </c>
-      <c r="S6" t="s">
-        <v>271</v>
-      </c>
-      <c r="T6" t="s">
-        <v>271</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>322</v>
       </c>
-      <c r="V6" t="s">
-        <v>323</v>
-      </c>
       <c r="W6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -3149,67 +3146,67 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" t="s">
         <v>324</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>325</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>326</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>327</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>267</v>
+      </c>
+      <c r="I7" t="s">
         <v>328</v>
       </c>
-      <c r="H7" t="s">
-        <v>268</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>329</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L7" t="s">
+        <v>270</v>
+      </c>
+      <c r="M7" t="s">
         <v>330</v>
       </c>
-      <c r="K7" t="s">
-        <v>271</v>
-      </c>
-      <c r="L7" t="s">
-        <v>271</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>331</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>332</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R7" t="s">
+        <v>270</v>
+      </c>
+      <c r="S7" t="s">
+        <v>270</v>
+      </c>
+      <c r="T7" t="s">
+        <v>270</v>
+      </c>
+      <c r="U7" t="s">
         <v>333</v>
       </c>
-      <c r="P7" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>271</v>
-      </c>
-      <c r="R7" t="s">
-        <v>271</v>
-      </c>
-      <c r="S7" t="s">
-        <v>271</v>
-      </c>
-      <c r="T7" t="s">
-        <v>271</v>
-      </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>334</v>
       </c>
-      <c r="V7" t="s">
-        <v>335</v>
-      </c>
       <c r="W7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -3220,67 +3217,67 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D8" t="s">
         <v>336</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>337</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>338</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>339</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>305</v>
+      </c>
+      <c r="I8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J8" t="s">
         <v>340</v>
       </c>
-      <c r="H8" t="s">
-        <v>306</v>
-      </c>
-      <c r="I8" t="s">
-        <v>307</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
+        <v>270</v>
+      </c>
+      <c r="L8" t="s">
+        <v>270</v>
+      </c>
+      <c r="M8" t="s">
+        <v>270</v>
+      </c>
+      <c r="N8" t="s">
+        <v>270</v>
+      </c>
+      <c r="O8" t="s">
+        <v>270</v>
+      </c>
+      <c r="P8" t="s">
         <v>341</v>
       </c>
-      <c r="K8" t="s">
-        <v>271</v>
-      </c>
-      <c r="L8" t="s">
-        <v>271</v>
-      </c>
-      <c r="M8" t="s">
-        <v>271</v>
-      </c>
-      <c r="N8" t="s">
-        <v>271</v>
-      </c>
-      <c r="O8" t="s">
-        <v>271</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>270</v>
+      </c>
+      <c r="R8" t="s">
+        <v>270</v>
+      </c>
+      <c r="S8" t="s">
+        <v>270</v>
+      </c>
+      <c r="T8" t="s">
+        <v>270</v>
+      </c>
+      <c r="U8" t="s">
         <v>342</v>
       </c>
-      <c r="Q8" t="s">
-        <v>271</v>
-      </c>
-      <c r="R8" t="s">
-        <v>271</v>
-      </c>
-      <c r="S8" t="s">
-        <v>271</v>
-      </c>
-      <c r="T8" t="s">
-        <v>271</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>343</v>
       </c>
-      <c r="V8" t="s">
-        <v>344</v>
-      </c>
       <c r="W8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
@@ -3291,67 +3288,67 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" t="s">
         <v>345</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>346</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>347</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>348</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>349</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>350</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>351</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
+        <v>270</v>
+      </c>
+      <c r="L9" t="s">
+        <v>270</v>
+      </c>
+      <c r="M9" t="s">
+        <v>270</v>
+      </c>
+      <c r="N9" t="s">
+        <v>270</v>
+      </c>
+      <c r="O9" t="s">
+        <v>270</v>
+      </c>
+      <c r="P9" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>270</v>
+      </c>
+      <c r="R9" t="s">
+        <v>270</v>
+      </c>
+      <c r="S9" t="s">
         <v>352</v>
       </c>
-      <c r="K9" t="s">
-        <v>271</v>
-      </c>
-      <c r="L9" t="s">
-        <v>271</v>
-      </c>
-      <c r="M9" t="s">
-        <v>271</v>
-      </c>
-      <c r="N9" t="s">
-        <v>271</v>
-      </c>
-      <c r="O9" t="s">
-        <v>271</v>
-      </c>
-      <c r="P9" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>271</v>
-      </c>
-      <c r="R9" t="s">
-        <v>271</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>353</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>354</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>355</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
         <v>356</v>
-      </c>
-      <c r="W9" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
@@ -3362,67 +3359,67 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D10" t="s">
         <v>358</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>359</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>360</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>361</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>281</v>
+      </c>
+      <c r="I10" t="s">
         <v>362</v>
       </c>
-      <c r="H10" t="s">
-        <v>282</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>363</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>364</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>365</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
+        <v>270</v>
+      </c>
+      <c r="N10" t="s">
+        <v>270</v>
+      </c>
+      <c r="O10" t="s">
+        <v>270</v>
+      </c>
+      <c r="P10" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>270</v>
+      </c>
+      <c r="R10" t="s">
+        <v>270</v>
+      </c>
+      <c r="S10" t="s">
+        <v>270</v>
+      </c>
+      <c r="T10" t="s">
+        <v>270</v>
+      </c>
+      <c r="U10" t="s">
         <v>366</v>
       </c>
-      <c r="M10" t="s">
-        <v>271</v>
-      </c>
-      <c r="N10" t="s">
-        <v>271</v>
-      </c>
-      <c r="O10" t="s">
-        <v>271</v>
-      </c>
-      <c r="P10" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>271</v>
-      </c>
-      <c r="R10" t="s">
-        <v>271</v>
-      </c>
-      <c r="S10" t="s">
-        <v>271</v>
-      </c>
-      <c r="T10" t="s">
-        <v>271</v>
-      </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>367</v>
       </c>
-      <c r="V10" t="s">
-        <v>368</v>
-      </c>
       <c r="W10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
@@ -3433,67 +3430,67 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" t="s">
         <v>369</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>370</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>371</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" t="s">
+        <v>267</v>
+      </c>
+      <c r="I11" t="s">
         <v>372</v>
       </c>
-      <c r="G11" t="s">
-        <v>340</v>
-      </c>
-      <c r="H11" t="s">
-        <v>268</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
+        <v>269</v>
+      </c>
+      <c r="K11" t="s">
+        <v>270</v>
+      </c>
+      <c r="L11" t="s">
+        <v>270</v>
+      </c>
+      <c r="M11" t="s">
         <v>373</v>
       </c>
-      <c r="J11" t="s">
-        <v>270</v>
-      </c>
-      <c r="K11" t="s">
-        <v>271</v>
-      </c>
-      <c r="L11" t="s">
-        <v>271</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>374</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
         <v>375</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>270</v>
+      </c>
+      <c r="R11" t="s">
+        <v>270</v>
+      </c>
+      <c r="S11" t="s">
+        <v>270</v>
+      </c>
+      <c r="T11" t="s">
+        <v>270</v>
+      </c>
+      <c r="U11" t="s">
         <v>376</v>
       </c>
-      <c r="P11" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>271</v>
-      </c>
-      <c r="R11" t="s">
-        <v>271</v>
-      </c>
-      <c r="S11" t="s">
-        <v>271</v>
-      </c>
-      <c r="T11" t="s">
-        <v>271</v>
-      </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>377</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
         <v>378</v>
-      </c>
-      <c r="W11" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
@@ -3504,67 +3501,67 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" t="s">
         <v>380</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>381</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>382</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>383</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>316</v>
+      </c>
+      <c r="I12" t="s">
         <v>384</v>
       </c>
-      <c r="H12" t="s">
-        <v>317</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
+        <v>318</v>
+      </c>
+      <c r="K12" t="s">
+        <v>270</v>
+      </c>
+      <c r="L12" t="s">
+        <v>270</v>
+      </c>
+      <c r="M12" t="s">
+        <v>270</v>
+      </c>
+      <c r="N12" t="s">
+        <v>270</v>
+      </c>
+      <c r="O12" t="s">
+        <v>270</v>
+      </c>
+      <c r="P12" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q12" t="s">
         <v>385</v>
       </c>
-      <c r="J12" t="s">
-        <v>319</v>
-      </c>
-      <c r="K12" t="s">
-        <v>271</v>
-      </c>
-      <c r="L12" t="s">
-        <v>271</v>
-      </c>
-      <c r="M12" t="s">
-        <v>271</v>
-      </c>
-      <c r="N12" t="s">
-        <v>271</v>
-      </c>
-      <c r="O12" t="s">
-        <v>271</v>
-      </c>
-      <c r="P12" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>386</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
+        <v>270</v>
+      </c>
+      <c r="T12" t="s">
+        <v>270</v>
+      </c>
+      <c r="U12" t="s">
         <v>387</v>
       </c>
-      <c r="S12" t="s">
-        <v>271</v>
-      </c>
-      <c r="T12" t="s">
-        <v>271</v>
-      </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
         <v>388</v>
       </c>
-      <c r="V12" t="s">
-        <v>389</v>
-      </c>
       <c r="W12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -3575,67 +3572,67 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D13" t="s">
         <v>390</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>391</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>392</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>393</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
+        <v>349</v>
+      </c>
+      <c r="I13" t="s">
         <v>394</v>
       </c>
-      <c r="H13" t="s">
-        <v>350</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>395</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
+        <v>270</v>
+      </c>
+      <c r="L13" t="s">
+        <v>270</v>
+      </c>
+      <c r="M13" t="s">
+        <v>270</v>
+      </c>
+      <c r="N13" t="s">
+        <v>270</v>
+      </c>
+      <c r="O13" t="s">
+        <v>270</v>
+      </c>
+      <c r="P13" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>270</v>
+      </c>
+      <c r="R13" t="s">
+        <v>270</v>
+      </c>
+      <c r="S13" t="s">
         <v>396</v>
       </c>
-      <c r="K13" t="s">
-        <v>271</v>
-      </c>
-      <c r="L13" t="s">
-        <v>271</v>
-      </c>
-      <c r="M13" t="s">
-        <v>271</v>
-      </c>
-      <c r="N13" t="s">
-        <v>271</v>
-      </c>
-      <c r="O13" t="s">
-        <v>271</v>
-      </c>
-      <c r="P13" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>271</v>
-      </c>
-      <c r="R13" t="s">
-        <v>271</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>397</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>398</v>
       </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
         <v>399</v>
       </c>
-      <c r="V13" t="s">
-        <v>400</v>
-      </c>
       <c r="W13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
@@ -3646,71 +3643,71 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>400</v>
+      </c>
+      <c r="D14" t="s">
         <v>401</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>402</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>403</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>404</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
+        <v>281</v>
+      </c>
+      <c r="I14" t="s">
         <v>405</v>
       </c>
-      <c r="H14" t="s">
-        <v>282</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
+        <v>294</v>
+      </c>
+      <c r="K14" t="s">
         <v>406</v>
       </c>
-      <c r="J14" t="s">
-        <v>295</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>407</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
+        <v>270</v>
+      </c>
+      <c r="N14" t="s">
+        <v>270</v>
+      </c>
+      <c r="O14" t="s">
+        <v>270</v>
+      </c>
+      <c r="P14" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>270</v>
+      </c>
+      <c r="R14" t="s">
+        <v>270</v>
+      </c>
+      <c r="S14" t="s">
+        <v>270</v>
+      </c>
+      <c r="T14" t="s">
+        <v>270</v>
+      </c>
+      <c r="U14" t="s">
         <v>408</v>
       </c>
-      <c r="M14" t="s">
-        <v>271</v>
-      </c>
-      <c r="N14" t="s">
-        <v>271</v>
-      </c>
-      <c r="O14" t="s">
-        <v>271</v>
-      </c>
-      <c r="P14" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>271</v>
-      </c>
-      <c r="R14" t="s">
-        <v>271</v>
-      </c>
-      <c r="S14" t="s">
-        <v>271</v>
-      </c>
-      <c r="T14" t="s">
-        <v>271</v>
-      </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
         <v>409</v>
       </c>
-      <c r="V14" t="s">
-        <v>410</v>
-      </c>
       <c r="W14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/샘플_신청데이터_10건.xlsx
+++ b/샘플_신청데이터_10건.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="400">
   <si>
     <t>접수번호</t>
   </si>
@@ -45,556 +45,526 @@
     <t>이메일</t>
   </si>
   <si>
+    <t>제공형태</t>
+  </si>
+  <si>
+    <t>제품분류</t>
+  </si>
+  <si>
+    <t>개요</t>
+  </si>
+  <si>
+    <t>인공지능적용목적</t>
+  </si>
+  <si>
+    <t>인공지능적용범위</t>
+  </si>
+  <si>
+    <t>구조도파일명</t>
+  </si>
+  <si>
+    <t>명세서작성방식</t>
+  </si>
+  <si>
+    <t>명세서파일명</t>
+  </si>
+  <si>
+    <t>기타제출서류파일명</t>
+  </si>
+  <si>
+    <t>보유인증</t>
+  </si>
+  <si>
+    <t>인증서파일명</t>
+  </si>
+  <si>
+    <t>열람이용동의여부</t>
+  </si>
+  <si>
+    <t>개인정보수집이용동의여부</t>
+  </si>
+  <si>
+    <t>개인정보3자제공동의여부</t>
+  </si>
+  <si>
+    <t>특기사항</t>
+  </si>
+  <si>
+    <t>AI202600001</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>㈜케이에이아이솔루션</t>
+  </si>
+  <si>
+    <t>123-45-67890</t>
+  </si>
+  <si>
+    <t>홍길동</t>
+  </si>
+  <si>
+    <t>서울특별시 송파구 올림픽로 300, 5층</t>
+  </si>
+  <si>
+    <t>김담당</t>
+  </si>
+  <si>
+    <t>02-2188-6980</t>
+  </si>
+  <si>
+    <t>ai-confirm@kaisol.example</t>
+  </si>
+  <si>
+    <t>SaaS(클라우드 서비스형)</t>
+  </si>
+  <si>
+    <t>소프트웨어</t>
+  </si>
+  <si>
+    <t>업무 문서를 업로드하면 본문을 분석하여 문서 유형을 자동 분류하고 담당 부서와 처리 우선순위를 추천하는 SaaS 기반 인공지능 서비스입니다.</t>
+  </si>
+  <si>
+    <t>비정형 문서 처리 시간을 단축하고 담당자 배정 및 분류 업무를 자동화하여 업무 효율을 높이는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>문서 업로드 후 텍스트 추출·전처리·분류 모델 추론·카테고리 추천·신뢰도 점수 산출 단계에 인공지능이 적용됩니다.</t>
+  </si>
+  <si>
+    <t>kaisol-architecture.pdf</t>
+  </si>
+  <si>
+    <t>직성제출</t>
+  </si>
+  <si>
+    <t>인공지능 신뢰성(CAT) 인증</t>
+  </si>
+  <si>
+    <t>cat-cert-0117.pdf</t>
+  </si>
+  <si>
+    <t>동의</t>
+  </si>
+  <si>
+    <t>미동의</t>
+  </si>
+  <si>
+    <t>AI202600002</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>주식회사 메디테크랩</t>
+  </si>
+  <si>
+    <t>234-56-78901</t>
+  </si>
+  <si>
+    <t>김대표</t>
+  </si>
+  <si>
+    <t>서울특별시 강남구 테헤란로 152</t>
+  </si>
+  <si>
+    <t>이담당</t>
+  </si>
+  <si>
+    <t>02-1234-5678</t>
+  </si>
+  <si>
+    <t>pilot@meditechlab.example</t>
+  </si>
+  <si>
+    <t>사내 구축형(온프레미스)</t>
+  </si>
+  <si>
+    <t>서비스</t>
+  </si>
+  <si>
+    <t>흉부 X-ray 영상에서 이상 소견을 탐지하고 판독 초안을 생성하는 영상판독 보조 서비스입니다.</t>
+  </si>
+  <si>
+    <t>판독 소요 시간을 단축하고 초기 스크리닝 정확도를 높이는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>영상 업로드 → 전처리 → 이상 탐지 모델 추론 → 위험도 분류 → 판독 소견 요약 생성 전 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>meditech-architecture.pdf</t>
+  </si>
+  <si>
+    <t>파일제출</t>
+  </si>
+  <si>
+    <t>meditech-spec.pdf</t>
+  </si>
+  <si>
+    <t>GS인증</t>
+  </si>
+  <si>
+    <t>gs-cert-0118.pdf</t>
+  </si>
+  <si>
+    <t>판독 결과는 참고용이며 최종 판단은 전문의가 수행합니다.</t>
+  </si>
+  <si>
+    <t>AI202600003</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>그린센서㈜</t>
+  </si>
+  <si>
+    <t>345-67-89012</t>
+  </si>
+  <si>
+    <t>박대표</t>
+  </si>
+  <si>
+    <t>전라북도 익산시 무왕로 895</t>
+  </si>
+  <si>
+    <t>최담당</t>
+  </si>
+  <si>
+    <t>063-555-0192</t>
+  </si>
+  <si>
+    <t>support@greensensor.example</t>
+  </si>
+  <si>
+    <t>기기</t>
+  </si>
+  <si>
+    <t>제품</t>
+  </si>
+  <si>
+    <t>온실 내 설치형 카메라 기기가 작물 잎 영상을 촬영·분석하여 병해충 발생을 조기 진단하는 온디바이스 인공지능 기기입니다.</t>
+  </si>
+  <si>
+    <t>병해충 조기 발견으로 농약 사용량을 줄이고 작물 수확량을 안정화하는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>카메라 촬영 → 엣지 보드 내 추론 → 병해충 분류 및 심각도 산출 → 관리 서버 알림 전송 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>greensensor-architecture.pdf</t>
+  </si>
+  <si>
+    <t>field-test-report.zip</t>
+  </si>
+  <si>
+    <t>AI202600004</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>㈜보이스브릿지</t>
+  </si>
+  <si>
+    <t>456-78-90123</t>
+  </si>
+  <si>
+    <t>정대표</t>
+  </si>
+  <si>
+    <t>경기도 성남시 분당구 판교로 255</t>
+  </si>
+  <si>
+    <t>한담당</t>
+  </si>
+  <si>
+    <t>031-777-0345</t>
+  </si>
+  <si>
+    <t>biz@voicebridge.example</t>
+  </si>
+  <si>
+    <t>상담 통화를 실시간 전사하고 상담 종료 시 요약문과 후속조치 항목을 자동 생성하는 콜센터 보조 서비스입니다.</t>
+  </si>
+  <si>
+    <t>상담원의 후처리 시간을 줄이고 상담 품질 관리 데이터를 축적하는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>음성 스트림 STT 전사 → 화자 분리 → 외부 LLM API 요약 생성 → 후속조치 분류 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>voicebridge-architecture.pdf</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>iso-cert-0120.pdf</t>
+  </si>
+  <si>
+    <t>AI202600005</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>로앤데이터㈜</t>
+  </si>
+  <si>
+    <t>567-89-01234</t>
+  </si>
+  <si>
+    <t>윤대표</t>
+  </si>
+  <si>
+    <t>서울특별시 서초구 서초대로 396</t>
+  </si>
+  <si>
+    <t>오담당</t>
+  </si>
+  <si>
+    <t>02-598-0417</t>
+  </si>
+  <si>
+    <t>contact@lawndata.example</t>
+  </si>
+  <si>
+    <t>자연어 질의로 판례·법령을 검색하고 관련도 순으로 요약을 제공하는 법률 검색 서비스입니다. 검색엔진과 오픈소스 임베딩 모델, 외부 LLM을 혼합 구성했습니다.</t>
+  </si>
+  <si>
+    <t>법률 전문가의 판례 조사 시간을 단축하는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>질의 임베딩 → 벡터 검색 → 재순위화 → 외부 LLM 요약 생성의 혼합형 인공지능 파이프라인이 적용됩니다.</t>
+  </si>
+  <si>
+    <t>lawndata-architecture.pdf</t>
+  </si>
+  <si>
+    <t>lawndata-spec.pdf</t>
+  </si>
+  <si>
+    <t>구성 요소별 상세는 명세서 파일 참조</t>
+  </si>
+  <si>
+    <t>AI202600006</t>
+  </si>
+  <si>
+    <t>인스펙타코리아㈜</t>
+  </si>
+  <si>
+    <t>678-90-12345</t>
+  </si>
+  <si>
+    <t>임대표</t>
+  </si>
+  <si>
+    <t>울산광역시 북구 산업로 915</t>
+  </si>
+  <si>
+    <t>서담당</t>
+  </si>
+  <si>
+    <t>052-289-0733</t>
+  </si>
+  <si>
+    <t>qc@inspecta.example</t>
+  </si>
+  <si>
+    <t>제조 라인 카메라 영상에서 부품 표면 결함을 실시간 검출하는 머신비전 검사 장비입니다.</t>
+  </si>
+  <si>
+    <t>육안 검사 의존도를 낮추고 불량 유출률을 감소시키는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>라인 카메라 촬영 → 전처리 → 자체 학습 결함검출 모델 추론 → 결함 분류·마킹 → MES 연동 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>inspecta-architecture.pdf</t>
+  </si>
+  <si>
+    <t>gs-cert-0122.pdf</t>
+  </si>
+  <si>
+    <t>AI202600007</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>㈜파인드로직</t>
+  </si>
+  <si>
+    <t>789-01-23456</t>
+  </si>
+  <si>
+    <t>장대표</t>
+  </si>
+  <si>
+    <t>대전광역시 유성구 대학로 291</t>
+  </si>
+  <si>
+    <t>노담당</t>
+  </si>
+  <si>
+    <t>042-330-0456</t>
+  </si>
+  <si>
+    <t>biz@findlogic.example</t>
+  </si>
+  <si>
+    <t>매장별 판매 이력과 외부 변수를 학습해 상품별 수요를 예측하는 리테일 분석 서비스입니다.</t>
+  </si>
+  <si>
+    <t>재고 과부족을 줄이고 발주 정확도를 높이는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>판매·기상·프로모션 데이터 수집 → 시계열 예측 모델 추론 → 상품별 수요량·안전재고 산출 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>findlogic-architecture.pdf</t>
+  </si>
+  <si>
+    <t>AI202600008</t>
+  </si>
+  <si>
+    <t>세이프비전㈜</t>
+  </si>
+  <si>
+    <t>890-12-34567</t>
+  </si>
+  <si>
+    <t>구대표</t>
+  </si>
+  <si>
+    <t>부산광역시 해운대구 센텀중앙로 79</t>
+  </si>
+  <si>
+    <t>표담당</t>
+  </si>
+  <si>
+    <t>051-720-0987</t>
+  </si>
+  <si>
+    <t>support@safevision.example</t>
+  </si>
+  <si>
+    <t>작업장 CCTV 영상을 실시간 분석해 안전모 미착용·위험구역 침입 등을 감지하는 온디바이스 안전관리 기기입니다.</t>
+  </si>
+  <si>
+    <t>산업재해를 예방하고 안전관리 인력 부담을 줄이는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>CCTV 스트림 → 엣지 추론 → 위험행동 분류 → 관제 서버 경보 전송 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>safevision-architecture.pdf</t>
+  </si>
+  <si>
+    <t>safevision-spec.pdf</t>
+  </si>
+  <si>
+    <t>safety-test.zip</t>
+  </si>
+  <si>
+    <t>cat-cert-0124.pdf</t>
+  </si>
+  <si>
+    <t>야간 저조도 환경 정확도는 별도 리포트 참조</t>
+  </si>
+  <si>
+    <t>AI202600009</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>링구아테크㈜</t>
+  </si>
+  <si>
+    <t>901-23-45678</t>
+  </si>
+  <si>
+    <t>문대표</t>
+  </si>
+  <si>
+    <t>서울특별시 마포구 월드컵북로 396</t>
+  </si>
+  <si>
+    <t>백담당</t>
+  </si>
+  <si>
+    <t>02-6000-0321</t>
+  </si>
+  <si>
+    <t>hello@linguatech.example</t>
+  </si>
+  <si>
+    <t>화상회의 음성을 실시간 전사·번역해 자막으로 제공하는 다국어 통역 서비스입니다. 자체 STT와 외부 번역 API를 혼합 구성했습니다.</t>
+  </si>
+  <si>
+    <t>다국어 회의의 소통 장벽을 낮추는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>음성 STT 전사 → 언어 감지 → 외부 번역 API 호출 → 자막 렌더링의 혼합형 파이프라인이 적용됩니다.</t>
+  </si>
+  <si>
+    <t>linguatech-architecture.pdf</t>
+  </si>
+  <si>
+    <t>iso-cert-0125.pdf</t>
+  </si>
+  <si>
+    <t>AI202600010</t>
+  </si>
+  <si>
+    <t>㈜바이오센스</t>
+  </si>
+  <si>
+    <t>012-34-56789</t>
+  </si>
+  <si>
+    <t>신대표</t>
+  </si>
+  <si>
+    <t>경기도 수원시 영통구 광교로 145</t>
+  </si>
+  <si>
+    <t>지담당</t>
+  </si>
+  <si>
+    <t>031-888-0654</t>
+  </si>
+  <si>
+    <t>contact@biosense.example</t>
+  </si>
+  <si>
+    <t>웨어러블에서 수집한 심전도 신호를 분석해 부정맥 등 이상 신호를 탐지하는 의료 보조 서비스입니다.</t>
+  </si>
+  <si>
+    <t>이상 신호 조기 발견으로 진단 보조 정확도를 높이는 것을 목적으로 합니다.</t>
+  </si>
+  <si>
+    <t>심전도 신호 수집 → 전처리 → 자체 학습 분류 모델 추론 → 이상 신호 등급·알림 산출 구간에 적용됩니다.</t>
+  </si>
+  <si>
+    <t>biosense-architecture.pdf</t>
+  </si>
+  <si>
+    <t>biosense-spec.pdf</t>
+  </si>
+  <si>
+    <t>gs-cert-0126.pdf</t>
+  </si>
+  <si>
+    <t>의료기기 인허가와는 별개의 인공지능 확인 신청건</t>
+  </si>
+  <si>
+    <t>연번</t>
+  </si>
+  <si>
     <t>제품 또는 서비스 모델명</t>
-  </si>
-  <si>
-    <t>제공형태</t>
-  </si>
-  <si>
-    <t>제품분류</t>
-  </si>
-  <si>
-    <t>개요</t>
-  </si>
-  <si>
-    <t>인공지능적용목적</t>
-  </si>
-  <si>
-    <t>인공지능적용범위</t>
-  </si>
-  <si>
-    <t>구조도파일명</t>
-  </si>
-  <si>
-    <t>명세서작성방식</t>
-  </si>
-  <si>
-    <t>명세서파일명</t>
-  </si>
-  <si>
-    <t>기타제출서류파일명</t>
-  </si>
-  <si>
-    <t>보유인증</t>
-  </si>
-  <si>
-    <t>인증서파일명</t>
-  </si>
-  <si>
-    <t>열람이용동의여부</t>
-  </si>
-  <si>
-    <t>개인정보수집이용동의여부</t>
-  </si>
-  <si>
-    <t>개인정보3자제공동의여부</t>
-  </si>
-  <si>
-    <t>특기사항</t>
-  </si>
-  <si>
-    <t>AI202600001</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>㈜케이에이아이솔루션</t>
-  </si>
-  <si>
-    <t>123-45-67890</t>
-  </si>
-  <si>
-    <t>홍길동</t>
-  </si>
-  <si>
-    <t>서울특별시 송파구 올림픽로 300, 5층</t>
-  </si>
-  <si>
-    <t>김담당</t>
-  </si>
-  <si>
-    <t>02-2188-6980</t>
-  </si>
-  <si>
-    <t>ai-confirm@kaisol.example</t>
-  </si>
-  <si>
-    <t>닥클래시파이</t>
-  </si>
-  <si>
-    <t>SaaS(클라우드 서비스형)</t>
-  </si>
-  <si>
-    <t>소프트웨어</t>
-  </si>
-  <si>
-    <t>업무 문서를 업로드하면 본문을 분석하여 문서 유형을 자동 분류하고 담당 부서와 처리 우선순위를 추천하는 SaaS 기반 인공지능 서비스입니다.</t>
-  </si>
-  <si>
-    <t>비정형 문서 처리 시간을 단축하고 담당자 배정 및 분류 업무를 자동화하여 업무 효율을 높이는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>문서 업로드 후 텍스트 추출·전처리·분류 모델 추론·카테고리 추천·신뢰도 점수 산출 단계에 인공지능이 적용됩니다.</t>
-  </si>
-  <si>
-    <t>kaisol-architecture.pdf</t>
-  </si>
-  <si>
-    <t>직성제출</t>
-  </si>
-  <si>
-    <t>인공지능 신뢰성(CAT) 인증</t>
-  </si>
-  <si>
-    <t>cat-cert-0117.pdf</t>
-  </si>
-  <si>
-    <t>동의</t>
-  </si>
-  <si>
-    <t>미동의</t>
-  </si>
-  <si>
-    <t>AI202600002</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>주식회사 메디테크랩</t>
-  </si>
-  <si>
-    <t>234-56-78901</t>
-  </si>
-  <si>
-    <t>김대표</t>
-  </si>
-  <si>
-    <t>서울특별시 강남구 테헤란로 152</t>
-  </si>
-  <si>
-    <t>이담당</t>
-  </si>
-  <si>
-    <t>02-1234-5678</t>
-  </si>
-  <si>
-    <t>pilot@meditechlab.example</t>
-  </si>
-  <si>
-    <t>메디뷰 판독보조</t>
-  </si>
-  <si>
-    <t>사내 구축형(온프레미스)</t>
-  </si>
-  <si>
-    <t>서비스</t>
-  </si>
-  <si>
-    <t>흉부 X-ray 영상에서 이상 소견을 탐지하고 판독 초안을 생성하는 영상판독 보조 서비스입니다.</t>
-  </si>
-  <si>
-    <t>판독 소요 시간을 단축하고 초기 스크리닝 정확도를 높이는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>영상 업로드 → 전처리 → 이상 탐지 모델 추론 → 위험도 분류 → 판독 소견 요약 생성 전 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>meditech-architecture.pdf</t>
-  </si>
-  <si>
-    <t>파일제출</t>
-  </si>
-  <si>
-    <t>meditech-spec.pdf</t>
-  </si>
-  <si>
-    <t>GS인증</t>
-  </si>
-  <si>
-    <t>gs-cert-0118.pdf</t>
-  </si>
-  <si>
-    <t>판독 결과는 참고용이며 최종 판단은 전문의가 수행합니다.</t>
-  </si>
-  <si>
-    <t>AI202600003</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>그린센서㈜</t>
-  </si>
-  <si>
-    <t>345-67-89012</t>
-  </si>
-  <si>
-    <t>박대표</t>
-  </si>
-  <si>
-    <t>전라북도 익산시 무왕로 895</t>
-  </si>
-  <si>
-    <t>최담당</t>
-  </si>
-  <si>
-    <t>063-555-0192</t>
-  </si>
-  <si>
-    <t>support@greensensor.example</t>
-  </si>
-  <si>
-    <t>스마트팜 병해충 진단기</t>
-  </si>
-  <si>
-    <t>기기</t>
-  </si>
-  <si>
-    <t>제품</t>
-  </si>
-  <si>
-    <t>온실 내 설치형 카메라 기기가 작물 잎 영상을 촬영·분석하여 병해충 발생을 조기 진단하는 온디바이스 인공지능 기기입니다.</t>
-  </si>
-  <si>
-    <t>병해충 조기 발견으로 농약 사용량을 줄이고 작물 수확량을 안정화하는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>카메라 촬영 → 엣지 보드 내 추론 → 병해충 분류 및 심각도 산출 → 관리 서버 알림 전송 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>greensensor-architecture.pdf</t>
-  </si>
-  <si>
-    <t>field-test-report.zip</t>
-  </si>
-  <si>
-    <t>AI202600004</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>㈜보이스브릿지</t>
-  </si>
-  <si>
-    <t>456-78-90123</t>
-  </si>
-  <si>
-    <t>정대표</t>
-  </si>
-  <si>
-    <t>경기도 성남시 분당구 판교로 255</t>
-  </si>
-  <si>
-    <t>한담당</t>
-  </si>
-  <si>
-    <t>031-777-0345</t>
-  </si>
-  <si>
-    <t>biz@voicebridge.example</t>
-  </si>
-  <si>
-    <t>콜센터 상담요약 어시스턴트</t>
-  </si>
-  <si>
-    <t>상담 통화를 실시간 전사하고 상담 종료 시 요약문과 후속조치 항목을 자동 생성하는 콜센터 보조 서비스입니다.</t>
-  </si>
-  <si>
-    <t>상담원의 후처리 시간을 줄이고 상담 품질 관리 데이터를 축적하는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>음성 스트림 STT 전사 → 화자 분리 → 외부 LLM API 요약 생성 → 후속조치 분류 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>voicebridge-architecture.pdf</t>
-  </si>
-  <si>
-    <t>기타</t>
-  </si>
-  <si>
-    <t>iso-cert-0120.pdf</t>
-  </si>
-  <si>
-    <t>AI202600005</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>로앤데이터㈜</t>
-  </si>
-  <si>
-    <t>567-89-01234</t>
-  </si>
-  <si>
-    <t>윤대표</t>
-  </si>
-  <si>
-    <t>서울특별시 서초구 서초대로 396</t>
-  </si>
-  <si>
-    <t>오담당</t>
-  </si>
-  <si>
-    <t>02-598-0417</t>
-  </si>
-  <si>
-    <t>contact@lawndata.example</t>
-  </si>
-  <si>
-    <t>리걸서치 판례검색</t>
-  </si>
-  <si>
-    <t>자연어 질의로 판례·법령을 검색하고 관련도 순으로 요약을 제공하는 법률 검색 서비스입니다. 검색엔진과 오픈소스 임베딩 모델, 외부 LLM을 혼합 구성했습니다.</t>
-  </si>
-  <si>
-    <t>법률 전문가의 판례 조사 시간을 단축하는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>질의 임베딩 → 벡터 검색 → 재순위화 → 외부 LLM 요약 생성의 혼합형 인공지능 파이프라인이 적용됩니다.</t>
-  </si>
-  <si>
-    <t>lawndata-architecture.pdf</t>
-  </si>
-  <si>
-    <t>lawndata-spec.pdf</t>
-  </si>
-  <si>
-    <t>구성 요소별 상세는 명세서 파일 참조</t>
-  </si>
-  <si>
-    <t>AI202600006</t>
-  </si>
-  <si>
-    <t>인스펙타코리아㈜</t>
-  </si>
-  <si>
-    <t>678-90-12345</t>
-  </si>
-  <si>
-    <t>임대표</t>
-  </si>
-  <si>
-    <t>울산광역시 북구 산업로 915</t>
-  </si>
-  <si>
-    <t>서담당</t>
-  </si>
-  <si>
-    <t>052-289-0733</t>
-  </si>
-  <si>
-    <t>qc@inspecta.example</t>
-  </si>
-  <si>
-    <t>품질검사 비전인식기</t>
-  </si>
-  <si>
-    <t>제조 라인 카메라 영상에서 부품 표면 결함을 실시간 검출하는 머신비전 검사 장비입니다.</t>
-  </si>
-  <si>
-    <t>육안 검사 의존도를 낮추고 불량 유출률을 감소시키는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>라인 카메라 촬영 → 전처리 → 자체 학습 결함검출 모델 추론 → 결함 분류·마킹 → MES 연동 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>inspecta-architecture.pdf</t>
-  </si>
-  <si>
-    <t>gs-cert-0122.pdf</t>
-  </si>
-  <si>
-    <t>AI202600007</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>㈜파인드로직</t>
-  </si>
-  <si>
-    <t>789-01-23456</t>
-  </si>
-  <si>
-    <t>장대표</t>
-  </si>
-  <si>
-    <t>대전광역시 유성구 대학로 291</t>
-  </si>
-  <si>
-    <t>노담당</t>
-  </si>
-  <si>
-    <t>042-330-0456</t>
-  </si>
-  <si>
-    <t>biz@findlogic.example</t>
-  </si>
-  <si>
-    <t>리테일 수요예측 엔진</t>
-  </si>
-  <si>
-    <t>매장별 판매 이력과 외부 변수를 학습해 상품별 수요를 예측하는 리테일 분석 서비스입니다.</t>
-  </si>
-  <si>
-    <t>재고 과부족을 줄이고 발주 정확도를 높이는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>판매·기상·프로모션 데이터 수집 → 시계열 예측 모델 추론 → 상품별 수요량·안전재고 산출 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>findlogic-architecture.pdf</t>
-  </si>
-  <si>
-    <t>AI202600008</t>
-  </si>
-  <si>
-    <t>세이프비전㈜</t>
-  </si>
-  <si>
-    <t>890-12-34567</t>
-  </si>
-  <si>
-    <t>구대표</t>
-  </si>
-  <si>
-    <t>부산광역시 해운대구 센텀중앙로 79</t>
-  </si>
-  <si>
-    <t>표담당</t>
-  </si>
-  <si>
-    <t>051-720-0987</t>
-  </si>
-  <si>
-    <t>support@safevision.example</t>
-  </si>
-  <si>
-    <t>산업안전 CCTV 위험행동 감지</t>
-  </si>
-  <si>
-    <t>작업장 CCTV 영상을 실시간 분석해 안전모 미착용·위험구역 침입 등을 감지하는 온디바이스 안전관리 기기입니다.</t>
-  </si>
-  <si>
-    <t>산업재해를 예방하고 안전관리 인력 부담을 줄이는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>CCTV 스트림 → 엣지 추론 → 위험행동 분류 → 관제 서버 경보 전송 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>safevision-architecture.pdf</t>
-  </si>
-  <si>
-    <t>safevision-spec.pdf</t>
-  </si>
-  <si>
-    <t>safety-test.zip</t>
-  </si>
-  <si>
-    <t>cat-cert-0124.pdf</t>
-  </si>
-  <si>
-    <t>야간 저조도 환경 정확도는 별도 리포트 참조</t>
-  </si>
-  <si>
-    <t>AI202600009</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>링구아테크㈜</t>
-  </si>
-  <si>
-    <t>901-23-45678</t>
-  </si>
-  <si>
-    <t>문대표</t>
-  </si>
-  <si>
-    <t>서울특별시 마포구 월드컵북로 396</t>
-  </si>
-  <si>
-    <t>백담당</t>
-  </si>
-  <si>
-    <t>02-6000-0321</t>
-  </si>
-  <si>
-    <t>hello@linguatech.example</t>
-  </si>
-  <si>
-    <t>실시간 다국어 회의 통역</t>
-  </si>
-  <si>
-    <t>화상회의 음성을 실시간 전사·번역해 자막으로 제공하는 다국어 통역 서비스입니다. 자체 STT와 외부 번역 API를 혼합 구성했습니다.</t>
-  </si>
-  <si>
-    <t>다국어 회의의 소통 장벽을 낮추는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>음성 STT 전사 → 언어 감지 → 외부 번역 API 호출 → 자막 렌더링의 혼합형 파이프라인이 적용됩니다.</t>
-  </si>
-  <si>
-    <t>linguatech-architecture.pdf</t>
-  </si>
-  <si>
-    <t>iso-cert-0125.pdf</t>
-  </si>
-  <si>
-    <t>AI202600010</t>
-  </si>
-  <si>
-    <t>㈜바이오센스</t>
-  </si>
-  <si>
-    <t>012-34-56789</t>
-  </si>
-  <si>
-    <t>신대표</t>
-  </si>
-  <si>
-    <t>경기도 수원시 영통구 광교로 145</t>
-  </si>
-  <si>
-    <t>지담당</t>
-  </si>
-  <si>
-    <t>031-888-0654</t>
-  </si>
-  <si>
-    <t>contact@biosense.example</t>
-  </si>
-  <si>
-    <t>심전도 이상 신호 분석기</t>
-  </si>
-  <si>
-    <t>웨어러블에서 수집한 심전도 신호를 분석해 부정맥 등 이상 신호를 탐지하는 의료 보조 서비스입니다.</t>
-  </si>
-  <si>
-    <t>이상 신호 조기 발견으로 진단 보조 정확도를 높이는 것을 목적으로 합니다.</t>
-  </si>
-  <si>
-    <t>심전도 신호 수집 → 전처리 → 자체 학습 분류 모델 추론 → 이상 신호 등급·알림 산출 구간에 적용됩니다.</t>
-  </si>
-  <si>
-    <t>biosense-architecture.pdf</t>
-  </si>
-  <si>
-    <t>biosense-spec.pdf</t>
-  </si>
-  <si>
-    <t>gs-cert-0126.pdf</t>
-  </si>
-  <si>
-    <t>의료기기 인허가와는 별개의 인공지능 확인 신청건</t>
-  </si>
-  <si>
-    <t>연번</t>
   </si>
   <si>
     <t>세부품명번호</t>
@@ -1622,20 +1592,20 @@
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="46" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
-    <col min="15" max="15" width="44" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="20" customWidth="1"/>
-    <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="8" customWidth="1"/>
-    <col min="23" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="34" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="46" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="44" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="8" customWidth="1"/>
+    <col min="22" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1711,700 +1681,667 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>34</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>38</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>39</v>
       </c>
-      <c r="P2" t="s">
+      <c r="S2" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" t="s">
         <v>41</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" t="s">
         <v>43</v>
-      </c>
-      <c r="V2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>48</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>51</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>52</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>53</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>54</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>55</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>56</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>57</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>58</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>59</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>60</v>
       </c>
-      <c r="P3" t="s">
+      <c r="S3" t="s">
         <v>61</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="T3" t="s">
         <v>62</v>
       </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" t="s">
         <v>63</v>
-      </c>
-      <c r="T3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" t="s">
-        <v>65</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
-      </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>68</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>71</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>72</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>73</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>74</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>75</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>76</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>77</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>78</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" t="s">
         <v>79</v>
       </c>
-      <c r="N4" t="s">
-        <v>80</v>
-      </c>
-      <c r="O4" t="s">
-        <v>81</v>
-      </c>
-      <c r="P4" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" t="s">
-        <v>83</v>
+      <c r="U4" t="s">
+        <v>42</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" t="s">
         <v>84</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
         <v>86</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>87</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>88</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" t="s">
         <v>89</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>90</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
         <v>91</v>
       </c>
-      <c r="I5" t="s">
+      <c r="O5" t="s">
         <v>92</v>
       </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" t="s">
         <v>93</v>
       </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="T5" t="s">
         <v>94</v>
       </c>
-      <c r="N5" t="s">
-        <v>95</v>
-      </c>
-      <c r="O5" t="s">
-        <v>96</v>
-      </c>
-      <c r="P5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" t="s">
-        <v>98</v>
-      </c>
       <c r="U5" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" t="s">
         <v>100</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G6" t="s">
         <v>101</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
         <v>102</v>
       </c>
-      <c r="D6" t="s">
+      <c r="I6" t="s">
         <v>103</v>
       </c>
-      <c r="E6" t="s">
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
         <v>104</v>
       </c>
-      <c r="F6" t="s">
+      <c r="M6" t="s">
         <v>105</v>
       </c>
-      <c r="G6" t="s">
+      <c r="N6" t="s">
         <v>106</v>
       </c>
-      <c r="H6" t="s">
+      <c r="O6" t="s">
         <v>107</v>
       </c>
-      <c r="I6" t="s">
+      <c r="P6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" t="s">
         <v>108</v>
       </c>
-      <c r="J6" t="s">
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="s">
         <v>109</v>
-      </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" t="s">
-        <v>110</v>
-      </c>
-      <c r="N6" t="s">
-        <v>111</v>
-      </c>
-      <c r="O6" t="s">
-        <v>112</v>
-      </c>
-      <c r="P6" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>62</v>
-      </c>
-      <c r="R6" t="s">
-        <v>114</v>
-      </c>
-      <c r="V6" t="s">
-        <v>44</v>
-      </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="I7" t="s">
         <v>117</v>
       </c>
-      <c r="D7" t="s">
+      <c r="J7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" t="s">
         <v>118</v>
       </c>
-      <c r="E7" t="s">
+      <c r="M7" t="s">
         <v>119</v>
       </c>
-      <c r="F7" t="s">
+      <c r="N7" t="s">
         <v>120</v>
       </c>
-      <c r="G7" t="s">
+      <c r="O7" t="s">
         <v>121</v>
       </c>
-      <c r="H7" t="s">
+      <c r="P7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S7" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" t="s">
         <v>122</v>
       </c>
-      <c r="I7" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" t="s">
-        <v>124</v>
-      </c>
-      <c r="K7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" t="s">
-        <v>125</v>
-      </c>
-      <c r="N7" t="s">
-        <v>126</v>
-      </c>
-      <c r="O7" t="s">
-        <v>127</v>
-      </c>
-      <c r="P7" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" t="s">
-        <v>64</v>
-      </c>
       <c r="U7" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" t="s">
         <v>130</v>
       </c>
-      <c r="B8" t="s">
+      <c r="I8" t="s">
         <v>131</v>
       </c>
-      <c r="C8" t="s">
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
         <v>132</v>
       </c>
-      <c r="D8" t="s">
+      <c r="M8" t="s">
         <v>133</v>
       </c>
-      <c r="E8" t="s">
+      <c r="N8" t="s">
         <v>134</v>
       </c>
-      <c r="F8" t="s">
+      <c r="O8" t="s">
         <v>135</v>
       </c>
-      <c r="G8" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" t="s">
-        <v>137</v>
-      </c>
-      <c r="I8" t="s">
-        <v>138</v>
-      </c>
-      <c r="J8" t="s">
-        <v>139</v>
-      </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" t="s">
-        <v>140</v>
-      </c>
-      <c r="N8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O8" t="s">
-        <v>142</v>
-      </c>
       <c r="P8" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="U8" t="s">
+        <v>42</v>
       </c>
       <c r="V8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W8" t="s">
-        <v>44</v>
-      </c>
-      <c r="X8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" t="s">
+        <v>143</v>
+      </c>
+      <c r="J9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" t="s">
         <v>144</v>
       </c>
-      <c r="B9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="M9" t="s">
         <v>145</v>
       </c>
-      <c r="D9" t="s">
+      <c r="N9" t="s">
         <v>146</v>
       </c>
-      <c r="E9" t="s">
+      <c r="O9" t="s">
         <v>147</v>
       </c>
-      <c r="F9" t="s">
+      <c r="P9" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q9" t="s">
         <v>148</v>
       </c>
-      <c r="G9" t="s">
+      <c r="R9" t="s">
         <v>149</v>
       </c>
-      <c r="H9" t="s">
+      <c r="S9" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" t="s">
         <v>150</v>
       </c>
-      <c r="I9" t="s">
+      <c r="U9" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" t="s">
         <v>151</v>
-      </c>
-      <c r="J9" t="s">
-        <v>152</v>
-      </c>
-      <c r="K9" t="s">
-        <v>77</v>
-      </c>
-      <c r="L9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M9" t="s">
-        <v>153</v>
-      </c>
-      <c r="N9" t="s">
-        <v>154</v>
-      </c>
-      <c r="O9" t="s">
-        <v>155</v>
-      </c>
-      <c r="P9" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>62</v>
-      </c>
-      <c r="R9" t="s">
-        <v>157</v>
-      </c>
-      <c r="S9" t="s">
-        <v>158</v>
-      </c>
-      <c r="T9" t="s">
-        <v>42</v>
-      </c>
-      <c r="U9" t="s">
-        <v>159</v>
-      </c>
-      <c r="V9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W9" t="s">
-        <v>44</v>
-      </c>
-      <c r="X9" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" t="s">
+        <v>160</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
         <v>161</v>
       </c>
-      <c r="B10" t="s">
+      <c r="M10" t="s">
         <v>162</v>
       </c>
-      <c r="C10" t="s">
+      <c r="N10" t="s">
         <v>163</v>
       </c>
-      <c r="D10" t="s">
+      <c r="O10" t="s">
         <v>164</v>
       </c>
-      <c r="E10" t="s">
+      <c r="P10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" t="s">
+        <v>93</v>
+      </c>
+      <c r="T10" t="s">
         <v>165</v>
       </c>
-      <c r="F10" t="s">
-        <v>166</v>
-      </c>
-      <c r="G10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I10" t="s">
-        <v>169</v>
-      </c>
-      <c r="J10" t="s">
-        <v>170</v>
-      </c>
-      <c r="K10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10" t="s">
-        <v>171</v>
-      </c>
-      <c r="N10" t="s">
-        <v>172</v>
-      </c>
-      <c r="O10" t="s">
-        <v>173</v>
-      </c>
-      <c r="P10" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>41</v>
-      </c>
-      <c r="T10" t="s">
-        <v>98</v>
-      </c>
       <c r="U10" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="V10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W10" t="s">
-        <v>44</v>
-      </c>
-      <c r="X10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H11" t="s">
+        <v>172</v>
+      </c>
+      <c r="I11" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
+        <v>174</v>
+      </c>
+      <c r="M11" t="s">
+        <v>175</v>
+      </c>
+      <c r="N11" t="s">
         <v>176</v>
       </c>
-      <c r="B11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="O11" t="s">
         <v>177</v>
       </c>
-      <c r="D11" t="s">
+      <c r="P11" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q11" t="s">
         <v>178</v>
       </c>
-      <c r="E11" t="s">
+      <c r="S11" t="s">
+        <v>61</v>
+      </c>
+      <c r="T11" t="s">
         <v>179</v>
       </c>
-      <c r="F11" t="s">
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11" t="s">
         <v>180</v>
-      </c>
-      <c r="G11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11" t="s">
-        <v>182</v>
-      </c>
-      <c r="I11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J11" t="s">
-        <v>184</v>
-      </c>
-      <c r="K11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11" t="s">
-        <v>185</v>
-      </c>
-      <c r="N11" t="s">
-        <v>186</v>
-      </c>
-      <c r="O11" t="s">
-        <v>187</v>
-      </c>
-      <c r="P11" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>62</v>
-      </c>
-      <c r="R11" t="s">
-        <v>189</v>
-      </c>
-      <c r="T11" t="s">
-        <v>64</v>
-      </c>
-      <c r="U11" t="s">
-        <v>190</v>
-      </c>
-      <c r="V11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W11" t="s">
-        <v>44</v>
-      </c>
-      <c r="X11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -2432,271 +2369,271 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E5" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D8" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E8" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D11" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="E11" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E12" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E14" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="E15" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E16" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2717,993 +2654,993 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J2" t="s">
+        <v>259</v>
+      </c>
+      <c r="K2" t="s">
+        <v>260</v>
+      </c>
+      <c r="L2" t="s">
+        <v>260</v>
+      </c>
+      <c r="M2" t="s">
+        <v>261</v>
+      </c>
+      <c r="N2" t="s">
         <v>262</v>
       </c>
-      <c r="D2" t="s">
+      <c r="O2" t="s">
+        <v>260</v>
+      </c>
+      <c r="P2" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>260</v>
+      </c>
+      <c r="R2" t="s">
+        <v>260</v>
+      </c>
+      <c r="S2" t="s">
+        <v>260</v>
+      </c>
+      <c r="T2" t="s">
+        <v>260</v>
+      </c>
+      <c r="U2" t="s">
         <v>263</v>
       </c>
-      <c r="E2" t="s">
+      <c r="V2" t="s">
         <v>264</v>
       </c>
-      <c r="F2" t="s">
+      <c r="W2" t="s">
         <v>265</v>
-      </c>
-      <c r="G2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I2" t="s">
-        <v>268</v>
-      </c>
-      <c r="J2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K2" t="s">
-        <v>270</v>
-      </c>
-      <c r="L2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M2" t="s">
-        <v>271</v>
-      </c>
-      <c r="N2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O2" t="s">
-        <v>270</v>
-      </c>
-      <c r="P2" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>270</v>
-      </c>
-      <c r="R2" t="s">
-        <v>270</v>
-      </c>
-      <c r="S2" t="s">
-        <v>270</v>
-      </c>
-      <c r="T2" t="s">
-        <v>270</v>
-      </c>
-      <c r="U2" t="s">
-        <v>273</v>
-      </c>
-      <c r="V2" t="s">
-        <v>274</v>
-      </c>
-      <c r="W2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I3" t="s">
+        <v>272</v>
+      </c>
+      <c r="J3" t="s">
+        <v>273</v>
+      </c>
+      <c r="K3" t="s">
+        <v>274</v>
+      </c>
+      <c r="L3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M3" t="s">
+        <v>260</v>
+      </c>
+      <c r="N3" t="s">
+        <v>260</v>
+      </c>
+      <c r="O3" t="s">
+        <v>260</v>
+      </c>
+      <c r="P3" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>260</v>
+      </c>
+      <c r="R3" t="s">
+        <v>260</v>
+      </c>
+      <c r="S3" t="s">
+        <v>260</v>
+      </c>
+      <c r="T3" t="s">
+        <v>260</v>
+      </c>
+      <c r="U3" t="s">
         <v>276</v>
       </c>
-      <c r="D3" t="s">
+      <c r="V3" t="s">
         <v>277</v>
       </c>
-      <c r="E3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G3" t="s">
-        <v>280</v>
-      </c>
-      <c r="H3" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" t="s">
-        <v>282</v>
-      </c>
-      <c r="J3" t="s">
-        <v>283</v>
-      </c>
-      <c r="K3" t="s">
-        <v>284</v>
-      </c>
-      <c r="L3" t="s">
-        <v>285</v>
-      </c>
-      <c r="M3" t="s">
-        <v>270</v>
-      </c>
-      <c r="N3" t="s">
-        <v>270</v>
-      </c>
-      <c r="O3" t="s">
-        <v>270</v>
-      </c>
-      <c r="P3" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>270</v>
-      </c>
-      <c r="R3" t="s">
-        <v>270</v>
-      </c>
-      <c r="S3" t="s">
-        <v>270</v>
-      </c>
-      <c r="T3" t="s">
-        <v>270</v>
-      </c>
-      <c r="U3" t="s">
-        <v>286</v>
-      </c>
-      <c r="V3" t="s">
-        <v>287</v>
-      </c>
       <c r="W3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K4" t="s">
+        <v>285</v>
+      </c>
+      <c r="L4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" t="s">
+        <v>260</v>
+      </c>
+      <c r="N4" t="s">
+        <v>260</v>
+      </c>
+      <c r="O4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P4" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>260</v>
+      </c>
+      <c r="R4" t="s">
+        <v>260</v>
+      </c>
+      <c r="S4" t="s">
+        <v>260</v>
+      </c>
+      <c r="T4" t="s">
+        <v>260</v>
+      </c>
+      <c r="U4" t="s">
+        <v>287</v>
+      </c>
+      <c r="V4" t="s">
         <v>288</v>
       </c>
-      <c r="D4" t="s">
+      <c r="W4" t="s">
         <v>289</v>
-      </c>
-      <c r="E4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" t="s">
-        <v>291</v>
-      </c>
-      <c r="G4" t="s">
-        <v>292</v>
-      </c>
-      <c r="H4" t="s">
-        <v>281</v>
-      </c>
-      <c r="I4" t="s">
-        <v>293</v>
-      </c>
-      <c r="J4" t="s">
-        <v>294</v>
-      </c>
-      <c r="K4" t="s">
-        <v>295</v>
-      </c>
-      <c r="L4" t="s">
-        <v>296</v>
-      </c>
-      <c r="M4" t="s">
-        <v>270</v>
-      </c>
-      <c r="N4" t="s">
-        <v>270</v>
-      </c>
-      <c r="O4" t="s">
-        <v>270</v>
-      </c>
-      <c r="P4" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>270</v>
-      </c>
-      <c r="R4" t="s">
-        <v>270</v>
-      </c>
-      <c r="S4" t="s">
-        <v>270</v>
-      </c>
-      <c r="T4" t="s">
-        <v>270</v>
-      </c>
-      <c r="U4" t="s">
-        <v>297</v>
-      </c>
-      <c r="V4" t="s">
-        <v>298</v>
-      </c>
-      <c r="W4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G5" t="s">
+        <v>294</v>
+      </c>
+      <c r="H5" t="s">
+        <v>295</v>
+      </c>
+      <c r="I5" t="s">
+        <v>296</v>
+      </c>
+      <c r="J5" t="s">
+        <v>297</v>
+      </c>
+      <c r="K5" t="s">
+        <v>260</v>
+      </c>
+      <c r="L5" t="s">
+        <v>260</v>
+      </c>
+      <c r="M5" t="s">
+        <v>260</v>
+      </c>
+      <c r="N5" t="s">
+        <v>260</v>
+      </c>
+      <c r="O5" t="s">
+        <v>260</v>
+      </c>
+      <c r="P5" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>260</v>
+      </c>
+      <c r="R5" t="s">
+        <v>260</v>
+      </c>
+      <c r="S5" t="s">
+        <v>260</v>
+      </c>
+      <c r="T5" t="s">
+        <v>260</v>
+      </c>
+      <c r="U5" t="s">
+        <v>299</v>
+      </c>
+      <c r="V5" t="s">
         <v>300</v>
       </c>
-      <c r="D5" t="s">
-        <v>301</v>
-      </c>
-      <c r="E5" t="s">
-        <v>302</v>
-      </c>
-      <c r="F5" t="s">
-        <v>303</v>
-      </c>
-      <c r="G5" t="s">
-        <v>304</v>
-      </c>
-      <c r="H5" t="s">
-        <v>305</v>
-      </c>
-      <c r="I5" t="s">
-        <v>306</v>
-      </c>
-      <c r="J5" t="s">
-        <v>307</v>
-      </c>
-      <c r="K5" t="s">
-        <v>270</v>
-      </c>
-      <c r="L5" t="s">
-        <v>270</v>
-      </c>
-      <c r="M5" t="s">
-        <v>270</v>
-      </c>
-      <c r="N5" t="s">
-        <v>270</v>
-      </c>
-      <c r="O5" t="s">
-        <v>270</v>
-      </c>
-      <c r="P5" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>270</v>
-      </c>
-      <c r="R5" t="s">
-        <v>270</v>
-      </c>
-      <c r="S5" t="s">
-        <v>270</v>
-      </c>
-      <c r="T5" t="s">
-        <v>270</v>
-      </c>
-      <c r="U5" t="s">
-        <v>309</v>
-      </c>
-      <c r="V5" t="s">
-        <v>310</v>
-      </c>
       <c r="W5" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>301</v>
+      </c>
+      <c r="D6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I6" t="s">
+        <v>307</v>
+      </c>
+      <c r="J6" t="s">
+        <v>308</v>
+      </c>
+      <c r="K6" t="s">
+        <v>260</v>
+      </c>
+      <c r="L6" t="s">
+        <v>260</v>
+      </c>
+      <c r="M6" t="s">
+        <v>260</v>
+      </c>
+      <c r="N6" t="s">
+        <v>260</v>
+      </c>
+      <c r="O6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P6" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>309</v>
+      </c>
+      <c r="R6" t="s">
+        <v>310</v>
+      </c>
+      <c r="S6" t="s">
+        <v>260</v>
+      </c>
+      <c r="T6" t="s">
+        <v>260</v>
+      </c>
+      <c r="U6" t="s">
         <v>311</v>
       </c>
-      <c r="D6" t="s">
+      <c r="V6" t="s">
         <v>312</v>
       </c>
-      <c r="E6" t="s">
-        <v>313</v>
-      </c>
-      <c r="F6" t="s">
-        <v>314</v>
-      </c>
-      <c r="G6" t="s">
-        <v>315</v>
-      </c>
-      <c r="H6" t="s">
-        <v>316</v>
-      </c>
-      <c r="I6" t="s">
-        <v>317</v>
-      </c>
-      <c r="J6" t="s">
-        <v>318</v>
-      </c>
-      <c r="K6" t="s">
-        <v>270</v>
-      </c>
-      <c r="L6" t="s">
-        <v>270</v>
-      </c>
-      <c r="M6" t="s">
-        <v>270</v>
-      </c>
-      <c r="N6" t="s">
-        <v>270</v>
-      </c>
-      <c r="O6" t="s">
-        <v>270</v>
-      </c>
-      <c r="P6" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>319</v>
-      </c>
-      <c r="R6" t="s">
-        <v>320</v>
-      </c>
-      <c r="S6" t="s">
-        <v>270</v>
-      </c>
-      <c r="T6" t="s">
-        <v>270</v>
-      </c>
-      <c r="U6" t="s">
-        <v>321</v>
-      </c>
-      <c r="V6" t="s">
-        <v>322</v>
-      </c>
       <c r="W6" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E7" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7" t="s">
+        <v>317</v>
+      </c>
+      <c r="H7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I7" t="s">
+        <v>318</v>
+      </c>
+      <c r="J7" t="s">
+        <v>319</v>
+      </c>
+      <c r="K7" t="s">
+        <v>260</v>
+      </c>
+      <c r="L7" t="s">
+        <v>260</v>
+      </c>
+      <c r="M7" t="s">
+        <v>320</v>
+      </c>
+      <c r="N7" t="s">
+        <v>321</v>
+      </c>
+      <c r="O7" t="s">
+        <v>322</v>
+      </c>
+      <c r="P7" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>260</v>
+      </c>
+      <c r="R7" t="s">
+        <v>260</v>
+      </c>
+      <c r="S7" t="s">
+        <v>260</v>
+      </c>
+      <c r="T7" t="s">
+        <v>260</v>
+      </c>
+      <c r="U7" t="s">
         <v>323</v>
       </c>
-      <c r="D7" t="s">
+      <c r="V7" t="s">
         <v>324</v>
       </c>
-      <c r="E7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F7" t="s">
-        <v>326</v>
-      </c>
-      <c r="G7" t="s">
-        <v>327</v>
-      </c>
-      <c r="H7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I7" t="s">
-        <v>328</v>
-      </c>
-      <c r="J7" t="s">
-        <v>329</v>
-      </c>
-      <c r="K7" t="s">
-        <v>270</v>
-      </c>
-      <c r="L7" t="s">
-        <v>270</v>
-      </c>
-      <c r="M7" t="s">
-        <v>330</v>
-      </c>
-      <c r="N7" t="s">
-        <v>331</v>
-      </c>
-      <c r="O7" t="s">
-        <v>332</v>
-      </c>
-      <c r="P7" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>270</v>
-      </c>
-      <c r="R7" t="s">
-        <v>270</v>
-      </c>
-      <c r="S7" t="s">
-        <v>270</v>
-      </c>
-      <c r="T7" t="s">
-        <v>270</v>
-      </c>
-      <c r="U7" t="s">
-        <v>333</v>
-      </c>
-      <c r="V7" t="s">
-        <v>334</v>
-      </c>
       <c r="W7" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E8" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F8" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="G8" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="H8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="I8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="J8" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="K8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P8" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="Q8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="T8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="U8" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="V8" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="W8" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F9" t="s">
+        <v>337</v>
+      </c>
+      <c r="G9" t="s">
+        <v>338</v>
+      </c>
+      <c r="H9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I9" t="s">
+        <v>340</v>
+      </c>
+      <c r="J9" t="s">
+        <v>341</v>
+      </c>
+      <c r="K9" t="s">
+        <v>260</v>
+      </c>
+      <c r="L9" t="s">
+        <v>260</v>
+      </c>
+      <c r="M9" t="s">
+        <v>260</v>
+      </c>
+      <c r="N9" t="s">
+        <v>260</v>
+      </c>
+      <c r="O9" t="s">
+        <v>260</v>
+      </c>
+      <c r="P9" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>260</v>
+      </c>
+      <c r="R9" t="s">
+        <v>260</v>
+      </c>
+      <c r="S9" t="s">
+        <v>342</v>
+      </c>
+      <c r="T9" t="s">
+        <v>343</v>
+      </c>
+      <c r="U9" t="s">
         <v>344</v>
       </c>
-      <c r="D9" t="s">
+      <c r="V9" t="s">
         <v>345</v>
       </c>
-      <c r="E9" t="s">
+      <c r="W9" t="s">
         <v>346</v>
-      </c>
-      <c r="F9" t="s">
-        <v>347</v>
-      </c>
-      <c r="G9" t="s">
-        <v>348</v>
-      </c>
-      <c r="H9" t="s">
-        <v>349</v>
-      </c>
-      <c r="I9" t="s">
-        <v>350</v>
-      </c>
-      <c r="J9" t="s">
-        <v>351</v>
-      </c>
-      <c r="K9" t="s">
-        <v>270</v>
-      </c>
-      <c r="L9" t="s">
-        <v>270</v>
-      </c>
-      <c r="M9" t="s">
-        <v>270</v>
-      </c>
-      <c r="N9" t="s">
-        <v>270</v>
-      </c>
-      <c r="O9" t="s">
-        <v>270</v>
-      </c>
-      <c r="P9" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>270</v>
-      </c>
-      <c r="R9" t="s">
-        <v>270</v>
-      </c>
-      <c r="S9" t="s">
-        <v>352</v>
-      </c>
-      <c r="T9" t="s">
-        <v>353</v>
-      </c>
-      <c r="U9" t="s">
-        <v>354</v>
-      </c>
-      <c r="V9" t="s">
-        <v>355</v>
-      </c>
-      <c r="W9" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" t="s">
+        <v>349</v>
+      </c>
+      <c r="F10" t="s">
+        <v>350</v>
+      </c>
+      <c r="G10" t="s">
+        <v>351</v>
+      </c>
+      <c r="H10" t="s">
+        <v>271</v>
+      </c>
+      <c r="I10" t="s">
+        <v>352</v>
+      </c>
+      <c r="J10" t="s">
+        <v>353</v>
+      </c>
+      <c r="K10" t="s">
+        <v>354</v>
+      </c>
+      <c r="L10" t="s">
+        <v>355</v>
+      </c>
+      <c r="M10" t="s">
+        <v>260</v>
+      </c>
+      <c r="N10" t="s">
+        <v>260</v>
+      </c>
+      <c r="O10" t="s">
+        <v>260</v>
+      </c>
+      <c r="P10" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>260</v>
+      </c>
+      <c r="R10" t="s">
+        <v>260</v>
+      </c>
+      <c r="S10" t="s">
+        <v>260</v>
+      </c>
+      <c r="T10" t="s">
+        <v>260</v>
+      </c>
+      <c r="U10" t="s">
+        <v>356</v>
+      </c>
+      <c r="V10" t="s">
         <v>357</v>
       </c>
-      <c r="D10" t="s">
-        <v>358</v>
-      </c>
-      <c r="E10" t="s">
-        <v>359</v>
-      </c>
-      <c r="F10" t="s">
-        <v>360</v>
-      </c>
-      <c r="G10" t="s">
-        <v>361</v>
-      </c>
-      <c r="H10" t="s">
-        <v>281</v>
-      </c>
-      <c r="I10" t="s">
-        <v>362</v>
-      </c>
-      <c r="J10" t="s">
-        <v>363</v>
-      </c>
-      <c r="K10" t="s">
-        <v>364</v>
-      </c>
-      <c r="L10" t="s">
-        <v>365</v>
-      </c>
-      <c r="M10" t="s">
-        <v>270</v>
-      </c>
-      <c r="N10" t="s">
-        <v>270</v>
-      </c>
-      <c r="O10" t="s">
-        <v>270</v>
-      </c>
-      <c r="P10" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>270</v>
-      </c>
-      <c r="R10" t="s">
-        <v>270</v>
-      </c>
-      <c r="S10" t="s">
-        <v>270</v>
-      </c>
-      <c r="T10" t="s">
-        <v>270</v>
-      </c>
-      <c r="U10" t="s">
-        <v>366</v>
-      </c>
-      <c r="V10" t="s">
-        <v>367</v>
-      </c>
       <c r="W10" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D11" t="s">
+        <v>359</v>
+      </c>
+      <c r="E11" t="s">
+        <v>360</v>
+      </c>
+      <c r="F11" t="s">
+        <v>361</v>
+      </c>
+      <c r="G11" t="s">
+        <v>329</v>
+      </c>
+      <c r="H11" t="s">
+        <v>257</v>
+      </c>
+      <c r="I11" t="s">
+        <v>362</v>
+      </c>
+      <c r="J11" t="s">
+        <v>259</v>
+      </c>
+      <c r="K11" t="s">
+        <v>260</v>
+      </c>
+      <c r="L11" t="s">
+        <v>260</v>
+      </c>
+      <c r="M11" t="s">
+        <v>363</v>
+      </c>
+      <c r="N11" t="s">
+        <v>364</v>
+      </c>
+      <c r="O11" t="s">
+        <v>365</v>
+      </c>
+      <c r="P11" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>260</v>
+      </c>
+      <c r="R11" t="s">
+        <v>260</v>
+      </c>
+      <c r="S11" t="s">
+        <v>260</v>
+      </c>
+      <c r="T11" t="s">
+        <v>260</v>
+      </c>
+      <c r="U11" t="s">
+        <v>366</v>
+      </c>
+      <c r="V11" t="s">
+        <v>367</v>
+      </c>
+      <c r="W11" t="s">
         <v>368</v>
-      </c>
-      <c r="D11" t="s">
-        <v>369</v>
-      </c>
-      <c r="E11" t="s">
-        <v>370</v>
-      </c>
-      <c r="F11" t="s">
-        <v>371</v>
-      </c>
-      <c r="G11" t="s">
-        <v>339</v>
-      </c>
-      <c r="H11" t="s">
-        <v>267</v>
-      </c>
-      <c r="I11" t="s">
-        <v>372</v>
-      </c>
-      <c r="J11" t="s">
-        <v>269</v>
-      </c>
-      <c r="K11" t="s">
-        <v>270</v>
-      </c>
-      <c r="L11" t="s">
-        <v>270</v>
-      </c>
-      <c r="M11" t="s">
-        <v>373</v>
-      </c>
-      <c r="N11" t="s">
-        <v>374</v>
-      </c>
-      <c r="O11" t="s">
-        <v>375</v>
-      </c>
-      <c r="P11" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>270</v>
-      </c>
-      <c r="R11" t="s">
-        <v>270</v>
-      </c>
-      <c r="S11" t="s">
-        <v>270</v>
-      </c>
-      <c r="T11" t="s">
-        <v>270</v>
-      </c>
-      <c r="U11" t="s">
-        <v>376</v>
-      </c>
-      <c r="V11" t="s">
-        <v>377</v>
-      </c>
-      <c r="W11" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D12" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="E12" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="F12" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="G12" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="H12" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="I12" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="J12" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="K12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="Q12" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="R12" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="S12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="T12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="U12" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="V12" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="W12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" t="s">
+        <v>380</v>
+      </c>
+      <c r="E13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F13" t="s">
+        <v>382</v>
+      </c>
+      <c r="G13" t="s">
+        <v>383</v>
+      </c>
+      <c r="H13" t="s">
+        <v>339</v>
+      </c>
+      <c r="I13" t="s">
+        <v>384</v>
+      </c>
+      <c r="J13" t="s">
+        <v>385</v>
+      </c>
+      <c r="K13" t="s">
+        <v>260</v>
+      </c>
+      <c r="L13" t="s">
+        <v>260</v>
+      </c>
+      <c r="M13" t="s">
+        <v>260</v>
+      </c>
+      <c r="N13" t="s">
+        <v>260</v>
+      </c>
+      <c r="O13" t="s">
+        <v>260</v>
+      </c>
+      <c r="P13" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>260</v>
+      </c>
+      <c r="R13" t="s">
+        <v>260</v>
+      </c>
+      <c r="S13" t="s">
+        <v>386</v>
+      </c>
+      <c r="T13" t="s">
+        <v>387</v>
+      </c>
+      <c r="U13" t="s">
+        <v>388</v>
+      </c>
+      <c r="V13" t="s">
         <v>389</v>
       </c>
-      <c r="D13" t="s">
-        <v>390</v>
-      </c>
-      <c r="E13" t="s">
-        <v>391</v>
-      </c>
-      <c r="F13" t="s">
-        <v>392</v>
-      </c>
-      <c r="G13" t="s">
-        <v>393</v>
-      </c>
-      <c r="H13" t="s">
-        <v>349</v>
-      </c>
-      <c r="I13" t="s">
-        <v>394</v>
-      </c>
-      <c r="J13" t="s">
-        <v>395</v>
-      </c>
-      <c r="K13" t="s">
-        <v>270</v>
-      </c>
-      <c r="L13" t="s">
-        <v>270</v>
-      </c>
-      <c r="M13" t="s">
-        <v>270</v>
-      </c>
-      <c r="N13" t="s">
-        <v>270</v>
-      </c>
-      <c r="O13" t="s">
-        <v>270</v>
-      </c>
-      <c r="P13" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>270</v>
-      </c>
-      <c r="R13" t="s">
-        <v>270</v>
-      </c>
-      <c r="S13" t="s">
-        <v>396</v>
-      </c>
-      <c r="T13" t="s">
-        <v>397</v>
-      </c>
-      <c r="U13" t="s">
-        <v>398</v>
-      </c>
-      <c r="V13" t="s">
-        <v>399</v>
-      </c>
       <c r="W13" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D14" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="E14" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="F14" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="G14" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="H14" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="I14" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="J14" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="K14" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="L14" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="M14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="N14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="P14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="Q14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="R14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="S14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="T14" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="U14" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="V14" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="W14" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
